--- a/human_resources_forms/009_exit_interview_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/009_exit_interview_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'burnout'}</t>
+          <t>burnout</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Burnout'}</t>
+          <t>Burnout</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'lack_of_challenge'}</t>
+          <t>lack_of_challenge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Lack of Challenge'}</t>
+          <t>Lack of Challenge</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'lack_of_autonomy'}</t>
+          <t>lack_of_autonomy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Lack of Autonomy'}</t>
+          <t>Lack of Autonomy</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'lack_of_growth_opportunities'}</t>
+          <t>lack_of_growth_opportunities</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Lack of Growth Opportunities'}</t>
+          <t>Lack of Growth Opportunities</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'no_reason'}</t>
+          <t>no_reason</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'No Reason'}</t>
+          <t>No Reason</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'improved_communication'}</t>
+          <t>improved_communication</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Improved Communication'}</t>
+          <t>Improved Communication</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'improved_management'}</t>
+          <t>improved_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Improved Management'}</t>
+          <t>Improved Management</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'improved_training'}</t>
+          <t>improved_training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Improved Training'}</t>
+          <t>Improved Training</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'improved_work-life_balance'}</t>
+          <t>improved_work-life_balance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Improved Work-Life Balance'}</t>
+          <t>Improved Work-Life Balance</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
